--- a/AI Planning/Job Scheduling/Flow Shop/problemset/problemset.xlsx
+++ b/AI Planning/Job Scheduling/Flow Shop/problemset/problemset.xlsx
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -531,13 +531,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="I2" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="M2" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -574,38 +574,38 @@
         <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Flow Shop/problemset/solution/ran/restaurante-10j-3m-5_60tr-constantd_ran.xlsx</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>30</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Flow Shop/problemset/solution/ran/restaurante-10j-3m-5_60tr-constantd_ran.xlsx</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>35</v>
-      </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Flow Shop/problemset/solution/neh/restaurante-10j-3m-5_60tr-constantd_neh.xlsx</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>30</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Flow Shop/problemset/solution/neh/restaurante-10j-3m-5_60tr-constantd_neh.xlsx</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>35</v>
-      </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>277</v>
+        <v>171</v>
       </c>
       <c r="M4" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -679,27 +679,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Flow Shop/problemset/solution/ran/restaurante-10j-3m-5_60tr-exponentiald_ran.xlsx</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>88</v>
+      </c>
+      <c r="I5" t="n">
         <v>30</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Flow Shop/problemset/solution/ran/restaurante-10j-3m-5_60tr-exponentiald_ran.xlsx</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>124</v>
-      </c>
-      <c r="I5" t="n">
-        <v>57</v>
-      </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="I6" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="J6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>136</v>
+        <v>339</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="I7" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>124</v>
+        <v>258</v>
       </c>
       <c r="M7" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="M8" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2026</v>
+        <v>1959</v>
       </c>
       <c r="E9" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1892</v>
+        <v>1873</v>
       </c>
       <c r="I9" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="J9" t="n">
         <v>200</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1792</v>
+        <v>1739</v>
       </c>
       <c r="M9" t="n">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1907</v>
+        <v>2006</v>
       </c>
       <c r="E11" t="n">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="I11" t="n">
-        <v>359</v>
+        <v>222</v>
       </c>
       <c r="J11" t="n">
         <v>200</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1715</v>
+        <v>1758</v>
       </c>
       <c r="M11" t="n">
-        <v>335</v>
+        <v>191</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1067</v>
+        <v>927</v>
       </c>
       <c r="E12" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1001</v>
+        <v>892</v>
       </c>
       <c r="I12" t="n">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="J12" t="n">
         <v>200</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>960</v>
+        <v>838</v>
       </c>
       <c r="M12" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="N12" t="n">
         <v>200</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1335</v>
+        <v>1044</v>
       </c>
       <c r="E13" t="n">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1306</v>
+        <v>1006</v>
       </c>
       <c r="I13" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="J13" t="n">
         <v>200</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1265</v>
+        <v>971</v>
       </c>
       <c r="M13" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="N13" t="n">
         <v>200</v>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2426</v>
+        <v>2892</v>
       </c>
       <c r="E14" t="n">
-        <v>711</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2426</v>
+        <v>2892</v>
       </c>
       <c r="I14" t="n">
-        <v>711</v>
+        <v>99</v>
       </c>
       <c r="J14" t="n">
         <v>200</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2426</v>
+        <v>2892</v>
       </c>
       <c r="M14" t="n">
-        <v>711</v>
+        <v>99</v>
       </c>
       <c r="N14" t="n">
         <v>200</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1771</v>
+        <v>1714</v>
       </c>
       <c r="E15" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1771</v>
+        <v>1714</v>
       </c>
       <c r="I15" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="J15" t="n">
         <v>200</v>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1771</v>
+        <v>1714</v>
       </c>
       <c r="M15" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N15" t="n">
         <v>200</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23031</v>
+        <v>22289</v>
       </c>
       <c r="E16" t="n">
-        <v>2525</v>
+        <v>1756</v>
       </c>
       <c r="F16" t="n">
         <v>800</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22196</v>
+        <v>22285</v>
       </c>
       <c r="I16" t="n">
-        <v>1849</v>
+        <v>1821</v>
       </c>
       <c r="J16" t="n">
         <v>800</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>21949</v>
+        <v>21709</v>
       </c>
       <c r="M16" t="n">
-        <v>2098</v>
+        <v>1594</v>
       </c>
       <c r="N16" t="n">
         <v>800</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23009</v>
+        <v>22271</v>
       </c>
       <c r="E18" t="n">
-        <v>1143</v>
+        <v>1460</v>
       </c>
       <c r="F18" t="n">
         <v>800</v>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22105</v>
+        <v>21644</v>
       </c>
       <c r="I18" t="n">
-        <v>1007</v>
+        <v>1204</v>
       </c>
       <c r="J18" t="n">
         <v>800</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>21712</v>
+        <v>21289</v>
       </c>
       <c r="M18" t="n">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="N18" t="n">
         <v>800</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12844</v>
+        <v>13202</v>
       </c>
       <c r="E19" t="n">
-        <v>755</v>
+        <v>1211</v>
       </c>
       <c r="F19" t="n">
         <v>800</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>12825</v>
+        <v>12731</v>
       </c>
       <c r="I19" t="n">
-        <v>740</v>
+        <v>1353</v>
       </c>
       <c r="J19" t="n">
         <v>800</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12299</v>
+        <v>12477</v>
       </c>
       <c r="M19" t="n">
-        <v>673</v>
+        <v>706</v>
       </c>
       <c r="N19" t="n">
         <v>800</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16269</v>
+        <v>16991</v>
       </c>
       <c r="E20" t="n">
-        <v>884</v>
+        <v>649</v>
       </c>
       <c r="F20" t="n">
         <v>800</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>16176</v>
+        <v>16607</v>
       </c>
       <c r="I20" t="n">
-        <v>967</v>
+        <v>687</v>
       </c>
       <c r="J20" t="n">
         <v>800</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15851</v>
+        <v>16334</v>
       </c>
       <c r="M20" t="n">
-        <v>903</v>
+        <v>670</v>
       </c>
       <c r="N20" t="n">
         <v>800</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31281</v>
+        <v>23231</v>
       </c>
       <c r="E21" t="n">
-        <v>1630</v>
+        <v>5022</v>
       </c>
       <c r="F21" t="n">
         <v>800</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31281</v>
+        <v>23231</v>
       </c>
       <c r="I21" t="n">
-        <v>1630</v>
+        <v>5022</v>
       </c>
       <c r="J21" t="n">
         <v>800</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>31281</v>
+        <v>23231</v>
       </c>
       <c r="M21" t="n">
-        <v>1630</v>
+        <v>5022</v>
       </c>
       <c r="N21" t="n">
         <v>800</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21550</v>
+        <v>21104</v>
       </c>
       <c r="E22" t="n">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F22" t="n">
         <v>800</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>21550</v>
+        <v>21104</v>
       </c>
       <c r="I22" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J22" t="n">
         <v>800</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>21550</v>
+        <v>21104</v>
       </c>
       <c r="M22" t="n">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="N22" t="n">
         <v>800</v>
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13196</v>
+        <v>12275</v>
       </c>
       <c r="E23" t="n">
-        <v>1228</v>
+        <v>1015</v>
       </c>
       <c r="F23" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12198</v>
+        <v>12069</v>
       </c>
       <c r="I23" t="n">
-        <v>1637</v>
+        <v>975</v>
       </c>
       <c r="J23" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>11979</v>
+        <v>11356</v>
       </c>
       <c r="M23" t="n">
-        <v>1402</v>
+        <v>941</v>
       </c>
       <c r="N23" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24">
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3570</v>
+        <v>3480</v>
       </c>
       <c r="E24" t="n">
-        <v>417</v>
+        <v>155</v>
       </c>
       <c r="F24" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3480</v>
+        <v>3330</v>
       </c>
       <c r="I24" t="n">
-        <v>505</v>
+        <v>163</v>
       </c>
       <c r="J24" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3450</v>
+        <v>3090</v>
       </c>
       <c r="M24" t="n">
-        <v>421</v>
+        <v>126</v>
       </c>
       <c r="N24" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25">
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12083</v>
+        <v>12495</v>
       </c>
       <c r="E25" t="n">
-        <v>1179</v>
+        <v>640</v>
       </c>
       <c r="F25" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>12140</v>
+        <v>11404</v>
       </c>
       <c r="I25" t="n">
-        <v>1555</v>
+        <v>724</v>
       </c>
       <c r="J25" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>11510</v>
+        <v>10794</v>
       </c>
       <c r="M25" t="n">
-        <v>1615</v>
+        <v>763</v>
       </c>
       <c r="N25" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7190</v>
+        <v>7378</v>
       </c>
       <c r="E26" t="n">
-        <v>1143</v>
+        <v>492</v>
       </c>
       <c r="F26" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6858</v>
+        <v>7046</v>
       </c>
       <c r="I26" t="n">
-        <v>1196</v>
+        <v>666</v>
       </c>
       <c r="J26" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6485</v>
+        <v>6642</v>
       </c>
       <c r="M26" t="n">
-        <v>573</v>
+        <v>518</v>
       </c>
       <c r="N26" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9603</v>
+        <v>9548</v>
       </c>
       <c r="E27" t="n">
-        <v>1050</v>
+        <v>951</v>
       </c>
       <c r="F27" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9065</v>
+        <v>9495</v>
       </c>
       <c r="I27" t="n">
-        <v>1015</v>
+        <v>689</v>
       </c>
       <c r="J27" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8851</v>
+        <v>8879</v>
       </c>
       <c r="M27" t="n">
-        <v>782</v>
+        <v>645</v>
       </c>
       <c r="N27" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16122</v>
+        <v>15517</v>
       </c>
       <c r="E28" t="n">
-        <v>415</v>
+        <v>1558</v>
       </c>
       <c r="F28" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>15887</v>
+        <v>14970</v>
       </c>
       <c r="I28" t="n">
-        <v>891</v>
+        <v>1402</v>
       </c>
       <c r="J28" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15840</v>
+        <v>14630</v>
       </c>
       <c r="M28" t="n">
-        <v>1964</v>
+        <v>1192</v>
       </c>
       <c r="N28" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13331</v>
+        <v>12536</v>
       </c>
       <c r="E29" t="n">
-        <v>1285</v>
+        <v>887</v>
       </c>
       <c r="F29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>12455</v>
+        <v>12467</v>
       </c>
       <c r="I29" t="n">
-        <v>1619</v>
+        <v>1187</v>
       </c>
       <c r="J29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>12197</v>
+        <v>12077</v>
       </c>
       <c r="M29" t="n">
-        <v>1021</v>
+        <v>760</v>
       </c>
       <c r="N29" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42606</v>
+        <v>45508</v>
       </c>
       <c r="E30" t="n">
-        <v>6209</v>
+        <v>3722</v>
       </c>
       <c r="F30" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>42677</v>
+        <v>44358</v>
       </c>
       <c r="I30" t="n">
-        <v>6502</v>
+        <v>4098</v>
       </c>
       <c r="J30" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>40602</v>
+        <v>41711</v>
       </c>
       <c r="M30" t="n">
-        <v>3785</v>
+        <v>5902</v>
       </c>
       <c r="N30" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31">
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M31" t="n">
         <v>12</v>
       </c>
       <c r="N31" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>44738</v>
+        <v>44721</v>
       </c>
       <c r="E32" t="n">
-        <v>5943</v>
+        <v>6320</v>
       </c>
       <c r="F32" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>41919</v>
+        <v>44465</v>
       </c>
       <c r="I32" t="n">
-        <v>7088</v>
+        <v>6454</v>
       </c>
       <c r="J32" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>38517</v>
+        <v>41052</v>
       </c>
       <c r="M32" t="n">
-        <v>6176</v>
+        <v>4624</v>
       </c>
       <c r="N32" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33">
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20106</v>
+        <v>19782</v>
       </c>
       <c r="E33" t="n">
-        <v>2692</v>
+        <v>3567</v>
       </c>
       <c r="F33" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18803</v>
+        <v>18070</v>
       </c>
       <c r="I33" t="n">
-        <v>2877</v>
+        <v>3083</v>
       </c>
       <c r="J33" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>17413</v>
+        <v>16496</v>
       </c>
       <c r="M33" t="n">
-        <v>2140</v>
+        <v>2611</v>
       </c>
       <c r="N33" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34">
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>24172</v>
+        <v>20980</v>
       </c>
       <c r="E34" t="n">
-        <v>2148</v>
+        <v>1939</v>
       </c>
       <c r="F34" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>23695</v>
+        <v>19917</v>
       </c>
       <c r="I34" t="n">
-        <v>2477</v>
+        <v>2015</v>
       </c>
       <c r="J34" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>21364</v>
+        <v>18070</v>
       </c>
       <c r="M34" t="n">
-        <v>2550</v>
+        <v>1724</v>
       </c>
       <c r="N34" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35">
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>68393</v>
+        <v>72067</v>
       </c>
       <c r="E35" t="n">
-        <v>15965</v>
+        <v>16632</v>
       </c>
       <c r="F35" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>66668</v>
+        <v>72324</v>
       </c>
       <c r="I35" t="n">
-        <v>16590</v>
+        <v>17550</v>
       </c>
       <c r="J35" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>65968</v>
+        <v>71372</v>
       </c>
       <c r="M35" t="n">
-        <v>11227</v>
+        <v>15613</v>
       </c>
       <c r="N35" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>42661</v>
+        <v>42127</v>
       </c>
       <c r="E36" t="n">
-        <v>4735</v>
+        <v>4699</v>
       </c>
       <c r="F36" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42295</v>
+        <v>41147</v>
       </c>
       <c r="I36" t="n">
-        <v>3568</v>
+        <v>4717</v>
       </c>
       <c r="J36" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>39159</v>
+        <v>37835</v>
       </c>
       <c r="M36" t="n">
-        <v>2582</v>
+        <v>3177</v>
       </c>
       <c r="N36" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="37">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3790</v>
+        <v>3891</v>
       </c>
       <c r="E37" t="n">
-        <v>461</v>
+        <v>318</v>
       </c>
       <c r="F37" t="n">
         <v>600</v>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3752</v>
+        <v>3736</v>
       </c>
       <c r="I37" t="n">
-        <v>454</v>
+        <v>379</v>
       </c>
       <c r="J37" t="n">
         <v>600</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3482</v>
+        <v>3529</v>
       </c>
       <c r="M37" t="n">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="N37" t="n">
         <v>600</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3648</v>
+        <v>3716</v>
       </c>
       <c r="E39" t="n">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="F39" t="n">
         <v>600</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3718</v>
+        <v>3596</v>
       </c>
       <c r="I39" t="n">
-        <v>411</v>
+        <v>368</v>
       </c>
       <c r="J39" t="n">
         <v>600</v>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3473</v>
+        <v>3432</v>
       </c>
       <c r="M39" t="n">
-        <v>427</v>
+        <v>309</v>
       </c>
       <c r="N39" t="n">
         <v>600</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1964</v>
+        <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="F40" t="n">
         <v>600</v>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1887</v>
+        <v>1905</v>
       </c>
       <c r="I40" t="n">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="J40" t="n">
         <v>600</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1730</v>
+        <v>1778</v>
       </c>
       <c r="M40" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="N40" t="n">
         <v>600</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3134</v>
+        <v>3124</v>
       </c>
       <c r="E41" t="n">
-        <v>462</v>
+        <v>406</v>
       </c>
       <c r="F41" t="n">
         <v>600</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3005</v>
+        <v>3037</v>
       </c>
       <c r="I41" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J41" t="n">
         <v>600</v>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2860</v>
+        <v>2853</v>
       </c>
       <c r="M41" t="n">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="N41" t="n">
         <v>600</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5233</v>
+        <v>5707</v>
       </c>
       <c r="E42" t="n">
-        <v>184</v>
+        <v>1153</v>
       </c>
       <c r="F42" t="n">
         <v>600</v>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5233</v>
+        <v>5707</v>
       </c>
       <c r="I42" t="n">
-        <v>184</v>
+        <v>1153</v>
       </c>
       <c r="J42" t="n">
         <v>600</v>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5233</v>
+        <v>5707</v>
       </c>
       <c r="M42" t="n">
-        <v>184</v>
+        <v>1153</v>
       </c>
       <c r="N42" t="n">
         <v>600</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3488</v>
+        <v>3716</v>
       </c>
       <c r="E43" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F43" t="n">
         <v>600</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3488</v>
+        <v>3716</v>
       </c>
       <c r="I43" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="J43" t="n">
         <v>600</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3488</v>
+        <v>3716</v>
       </c>
       <c r="M43" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="N43" t="n">
         <v>600</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28859</v>
+        <v>28697</v>
       </c>
       <c r="E44" t="n">
-        <v>1723</v>
+        <v>2945</v>
       </c>
       <c r="F44" t="n">
         <v>4500</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>28511</v>
+        <v>28119</v>
       </c>
       <c r="I44" t="n">
-        <v>1958</v>
+        <v>2074</v>
       </c>
       <c r="J44" t="n">
         <v>4500</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28615</v>
+        <v>28352</v>
       </c>
       <c r="E46" t="n">
-        <v>1800</v>
+        <v>2440</v>
       </c>
       <c r="F46" t="n">
         <v>4500</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>28050</v>
+        <v>28040</v>
       </c>
       <c r="I46" t="n">
-        <v>1719</v>
+        <v>2389</v>
       </c>
       <c r="J46" t="n">
         <v>4500</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13561</v>
+        <v>13385</v>
       </c>
       <c r="E47" t="n">
-        <v>1018</v>
+        <v>1231</v>
       </c>
       <c r="F47" t="n">
         <v>4500</v>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>13296</v>
+        <v>13125</v>
       </c>
       <c r="I47" t="n">
-        <v>1395</v>
+        <v>1231</v>
       </c>
       <c r="J47" t="n">
         <v>4500</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18918</v>
+        <v>20336</v>
       </c>
       <c r="E48" t="n">
-        <v>1313</v>
+        <v>1347</v>
       </c>
       <c r="F48" t="n">
         <v>4500</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>18673</v>
+        <v>19861</v>
       </c>
       <c r="I48" t="n">
-        <v>1139</v>
+        <v>1154</v>
       </c>
       <c r="J48" t="n">
         <v>4500</v>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>46411</v>
+        <v>47339</v>
       </c>
       <c r="E49" t="n">
-        <v>12978</v>
+        <v>19145</v>
       </c>
       <c r="F49" t="n">
         <v>4500</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>46411</v>
+        <v>47339</v>
       </c>
       <c r="I49" t="n">
-        <v>12978</v>
+        <v>19145</v>
       </c>
       <c r="J49" t="n">
         <v>4500</v>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>26557</v>
+        <v>26029</v>
       </c>
       <c r="E50" t="n">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="F50" t="n">
         <v>4500</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>26557</v>
+        <v>26029</v>
       </c>
       <c r="I50" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J50" t="n">
         <v>4500</v>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>296786</v>
+        <v>306022</v>
       </c>
       <c r="E51" t="n">
-        <v>16571</v>
+        <v>11145</v>
       </c>
       <c r="F51" t="n">
         <v>3000</v>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>293585</v>
+        <v>298078</v>
       </c>
       <c r="I51" t="n">
-        <v>18155</v>
+        <v>11312</v>
       </c>
       <c r="J51" t="n">
         <v>3000</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>292062</v>
+        <v>295635</v>
       </c>
       <c r="E53" t="n">
-        <v>13930</v>
+        <v>16389</v>
       </c>
       <c r="F53" t="n">
         <v>3000</v>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>287413</v>
+        <v>287806</v>
       </c>
       <c r="I53" t="n">
-        <v>14827</v>
+        <v>15618</v>
       </c>
       <c r="J53" t="n">
         <v>3000</v>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>152580</v>
+        <v>152519</v>
       </c>
       <c r="E54" t="n">
-        <v>7444</v>
+        <v>11304</v>
       </c>
       <c r="F54" t="n">
         <v>3000</v>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>148620</v>
+        <v>149570</v>
       </c>
       <c r="I54" t="n">
-        <v>8438</v>
+        <v>9625</v>
       </c>
       <c r="J54" t="n">
         <v>3000</v>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>209652</v>
+        <v>195156</v>
       </c>
       <c r="E55" t="n">
-        <v>9222</v>
+        <v>6517</v>
       </c>
       <c r="F55" t="n">
         <v>3000</v>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>206851</v>
+        <v>191735</v>
       </c>
       <c r="I55" t="n">
-        <v>9017</v>
+        <v>8260</v>
       </c>
       <c r="J55" t="n">
         <v>3000</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>471391</v>
+        <v>339829</v>
       </c>
       <c r="E56" t="n">
-        <v>3828</v>
+        <v>112285</v>
       </c>
       <c r="F56" t="n">
         <v>3000</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>471391</v>
+        <v>339829</v>
       </c>
       <c r="I56" t="n">
-        <v>3828</v>
+        <v>112285</v>
       </c>
       <c r="J56" t="n">
         <v>3000</v>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>283251</v>
+        <v>276474</v>
       </c>
       <c r="E57" t="n">
-        <v>5488</v>
+        <v>5484</v>
       </c>
       <c r="F57" t="n">
         <v>3000</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>283251</v>
+        <v>276474</v>
       </c>
       <c r="I57" t="n">
-        <v>5476</v>
+        <v>5437</v>
       </c>
       <c r="J57" t="n">
         <v>3000</v>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>56361</v>
+        <v>56625</v>
       </c>
       <c r="E58" t="n">
-        <v>2628</v>
+        <v>3640</v>
       </c>
       <c r="F58" t="n">
         <v>8000</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>55504</v>
+        <v>55469</v>
       </c>
       <c r="I58" t="n">
-        <v>2637</v>
+        <v>3530</v>
       </c>
       <c r="J58" t="n">
         <v>8000</v>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>55565</v>
+        <v>55035</v>
       </c>
       <c r="E60" t="n">
-        <v>2173</v>
+        <v>2105</v>
       </c>
       <c r="F60" t="n">
         <v>8000</v>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>54907</v>
+        <v>55189</v>
       </c>
       <c r="I60" t="n">
-        <v>2059</v>
+        <v>1568</v>
       </c>
       <c r="J60" t="n">
         <v>8000</v>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26135</v>
+        <v>25475</v>
       </c>
       <c r="E61" t="n">
-        <v>1779</v>
+        <v>2135</v>
       </c>
       <c r="F61" t="n">
         <v>8000</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>25531</v>
+        <v>25057</v>
       </c>
       <c r="I61" t="n">
-        <v>1539</v>
+        <v>1767</v>
       </c>
       <c r="J61" t="n">
         <v>8000</v>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>36997</v>
+        <v>31524</v>
       </c>
       <c r="E62" t="n">
-        <v>1602</v>
+        <v>1167</v>
       </c>
       <c r="F62" t="n">
         <v>8000</v>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36736</v>
+        <v>31234</v>
       </c>
       <c r="I62" t="n">
-        <v>1677</v>
+        <v>1115</v>
       </c>
       <c r="J62" t="n">
         <v>8000</v>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>97235</v>
+        <v>96398</v>
       </c>
       <c r="E63" t="n">
-        <v>332</v>
+        <v>32961</v>
       </c>
       <c r="F63" t="n">
         <v>8000</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>97235</v>
+        <v>96398</v>
       </c>
       <c r="I63" t="n">
-        <v>332</v>
+        <v>32961</v>
       </c>
       <c r="J63" t="n">
         <v>8000</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>53130</v>
+        <v>51736</v>
       </c>
       <c r="E64" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F64" t="n">
         <v>8000</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>53130</v>
+        <v>51736</v>
       </c>
       <c r="I64" t="n">
         <v>739</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>56272</v>
+        <v>56473</v>
       </c>
       <c r="E65" t="n">
-        <v>2692</v>
+        <v>3140</v>
       </c>
       <c r="F65" t="n">
         <v>8000</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>55869</v>
+        <v>55590</v>
       </c>
       <c r="I65" t="n">
-        <v>2431</v>
+        <v>2752</v>
       </c>
       <c r="J65" t="n">
         <v>8000</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>55678</v>
+        <v>55259</v>
       </c>
       <c r="E67" t="n">
-        <v>2443</v>
+        <v>2229</v>
       </c>
       <c r="F67" t="n">
         <v>8000</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>54576</v>
+        <v>54483</v>
       </c>
       <c r="I67" t="n">
-        <v>2687</v>
+        <v>2399</v>
       </c>
       <c r="J67" t="n">
         <v>8000</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>26367</v>
+        <v>25973</v>
       </c>
       <c r="E68" t="n">
-        <v>1705</v>
+        <v>1817</v>
       </c>
       <c r="F68" t="n">
         <v>8000</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>25888</v>
+        <v>25336</v>
       </c>
       <c r="I68" t="n">
-        <v>1640</v>
+        <v>2035</v>
       </c>
       <c r="J68" t="n">
         <v>8000</v>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>33467</v>
+        <v>34195</v>
       </c>
       <c r="E69" t="n">
-        <v>1066</v>
+        <v>1370</v>
       </c>
       <c r="F69" t="n">
         <v>8000</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>32934</v>
+        <v>33826</v>
       </c>
       <c r="I69" t="n">
-        <v>1063</v>
+        <v>1268</v>
       </c>
       <c r="J69" t="n">
         <v>8000</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>72328</v>
+        <v>94292</v>
       </c>
       <c r="E70" t="n">
-        <v>31369</v>
+        <v>27858</v>
       </c>
       <c r="F70" t="n">
         <v>8000</v>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>72328</v>
+        <v>94292</v>
       </c>
       <c r="I70" t="n">
-        <v>31369</v>
+        <v>27858</v>
       </c>
       <c r="J70" t="n">
         <v>8000</v>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>52606</v>
+        <v>53315</v>
       </c>
       <c r="E71" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F71" t="n">
         <v>8000</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>52606</v>
+        <v>53315</v>
       </c>
       <c r="I71" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J71" t="n">
         <v>8000</v>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>573274</v>
+        <v>571372</v>
       </c>
       <c r="E72" t="n">
-        <v>50851</v>
+        <v>45482</v>
       </c>
       <c r="F72" t="n">
         <v>18000</v>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>560964</v>
+        <v>568514</v>
       </c>
       <c r="I72" t="n">
-        <v>47093</v>
+        <v>43794</v>
       </c>
       <c r="J72" t="n">
         <v>18000</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>564403</v>
+        <v>558788</v>
       </c>
       <c r="E74" t="n">
-        <v>45780</v>
+        <v>50569</v>
       </c>
       <c r="F74" t="n">
         <v>18000</v>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>557456</v>
+        <v>553948</v>
       </c>
       <c r="I74" t="n">
-        <v>45916</v>
+        <v>46795</v>
       </c>
       <c r="J74" t="n">
         <v>18000</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>248745</v>
+        <v>246360</v>
       </c>
       <c r="E75" t="n">
-        <v>32668</v>
+        <v>27860</v>
       </c>
       <c r="F75" t="n">
         <v>18000</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>238705</v>
+        <v>241864</v>
       </c>
       <c r="I75" t="n">
-        <v>34386</v>
+        <v>32232</v>
       </c>
       <c r="J75" t="n">
         <v>18000</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>318094</v>
+        <v>322171</v>
       </c>
       <c r="E76" t="n">
-        <v>22118</v>
+        <v>20175</v>
       </c>
       <c r="F76" t="n">
         <v>18000</v>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>314740</v>
+        <v>321030</v>
       </c>
       <c r="I76" t="n">
-        <v>23141</v>
+        <v>22349</v>
       </c>
       <c r="J76" t="n">
         <v>18000</v>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>970177</v>
+        <v>825462</v>
       </c>
       <c r="E77" t="n">
-        <v>454193</v>
+        <v>267520</v>
       </c>
       <c r="F77" t="n">
         <v>18000</v>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>970177</v>
+        <v>825462</v>
       </c>
       <c r="I77" t="n">
-        <v>454193</v>
+        <v>267520</v>
       </c>
       <c r="J77" t="n">
         <v>18000</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>526712</v>
+        <v>511300</v>
       </c>
       <c r="E78" t="n">
-        <v>17390</v>
+        <v>17350</v>
       </c>
       <c r="F78" t="n">
         <v>18000</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>526712</v>
+        <v>511300</v>
       </c>
       <c r="I78" t="n">
-        <v>17455</v>
+        <v>17315</v>
       </c>
       <c r="J78" t="n">
         <v>18000</v>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>61425</v>
+        <v>62094</v>
       </c>
       <c r="E79" t="n">
-        <v>16215</v>
+        <v>15560</v>
       </c>
       <c r="F79" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>60975</v>
+        <v>61153</v>
       </c>
       <c r="I79" t="n">
-        <v>15665</v>
+        <v>15703</v>
       </c>
       <c r="J79" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -4369,13 +4369,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F80" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4383,13 +4383,13 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="I80" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J80" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>60438</v>
+        <v>59795</v>
       </c>
       <c r="E81" t="n">
-        <v>14725</v>
+        <v>14348</v>
       </c>
       <c r="F81" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4427,13 +4427,13 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>59431</v>
+        <v>59420</v>
       </c>
       <c r="I81" t="n">
-        <v>15231</v>
+        <v>14038</v>
       </c>
       <c r="J81" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>29014</v>
+        <v>28693</v>
       </c>
       <c r="E82" t="n">
-        <v>9164</v>
+        <v>9345</v>
       </c>
       <c r="F82" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>28453</v>
+        <v>28479</v>
       </c>
       <c r="I82" t="n">
-        <v>9528</v>
+        <v>9036</v>
       </c>
       <c r="J82" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -4501,13 +4501,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27917</v>
+        <v>30147</v>
       </c>
       <c r="E83" t="n">
-        <v>6295</v>
+        <v>6959</v>
       </c>
       <c r="F83" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4515,13 +4515,13 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>27410</v>
+        <v>29720</v>
       </c>
       <c r="I83" t="n">
-        <v>5956</v>
+        <v>6754</v>
       </c>
       <c r="J83" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>86015</v>
+        <v>87588</v>
       </c>
       <c r="E84" t="n">
-        <v>40957</v>
+        <v>34571</v>
       </c>
       <c r="F84" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>84743</v>
+        <v>85833</v>
       </c>
       <c r="I84" t="n">
-        <v>40666</v>
+        <v>33832</v>
       </c>
       <c r="J84" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>55908</v>
+        <v>57351</v>
       </c>
       <c r="E85" t="n">
-        <v>13071</v>
+        <v>13380</v>
       </c>
       <c r="F85" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>55250</v>
+        <v>56829</v>
       </c>
       <c r="I85" t="n">
-        <v>13068</v>
+        <v>13615</v>
       </c>
       <c r="J85" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
